--- a/PCA.xlsx
+++ b/PCA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3cd4c70924fc60/เอกสาร/GitHub/Avian-Communities-Belihuloya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_B89231273C19EEB0D496B9981F1C06A2CADD4052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D47AC3-431E-4840-B5F8-4118297529AB}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_B89231273C19EEB0D496B9981F1C06A2CADD4052" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B24DC8-40A8-4A41-902C-225F2C3CF65E}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -358,9 +358,6 @@
     <t>Black eagle, Indian swiftlet, Asian palm swift</t>
   </si>
   <si>
-    <t>Green Wabbler, Scimitter Babbler</t>
-  </si>
-  <si>
     <t>Indian peafowl, Indian swiftlet, Common Tailorbird, Brown capped Babbler</t>
   </si>
   <si>
@@ -418,9 +415,6 @@
     <t>Jungle fowl, Chestnut backed Owlet, Indian swiftlet, Yellow fronted Barbet, Yellow eared Bulbul, Spot winged Thrush, White rumped Shama, Brown breasted Flycatcher, Tickell's blue Flycatcher, Sri Lankan whiteye</t>
   </si>
   <si>
-    <t>King quail, Black eagle, Brown headed barbet, Paddyfield Pipit, Zitting cisticola, Brown capped Babbler, Sri Lankan whiteye</t>
-  </si>
-  <si>
     <t>Spurfowl, Jungle fowl, White bellied sea eagle, Alexandrian parakeet, Orange minivet, Large billed leaf wabbler</t>
   </si>
   <si>
@@ -472,18 +466,12 @@
     <t>Jungle fowl, Brown capped Babbler, Scimitter Babbler, Spot winged Thrush, White rumped Shama</t>
   </si>
   <si>
-    <t>Yellow fronted Barbet, Brown capped Babbler</t>
-  </si>
-  <si>
     <t>Spotted Dove, Sri Lanka Hanging Parrot, Common Iora, Black hooded Oriole, Red vented Bulbul, Yellow billed Babbler</t>
   </si>
   <si>
     <t>Spotted Dove, Sri Lanka Hanging Parrot, Yellow fronted Barbet, Crimson fronted Barbet, Common Iora, Black hooded Oriole, Black capped Bulbul, White browed Bulbul, Square tailed bulbul, Ashy Prinia, Common Tailorbird, Large billed leaf wabbler, Brown capped Babbler, Yellow billed Babbler, White rumped Shama, Tickell's blue Flycatcher, Oriental whiteye</t>
   </si>
   <si>
-    <t>Spotted Dove, Sri Lanka Hanging Parrot, Drongo cuckoo, Crimson fronted Barbet, Copper smith Barbet, Common Iora, Large billed leaf wabbler, White rumped Shama, Asian brown Flycatcher, Pale billed Flowerpecker</t>
-  </si>
-  <si>
     <t>Sri Lanka Hanging Parrot, Yellow fronted Barbet, Common Iora, Green Wabbler, Tickell's blue Flycatcher, Oriental whiteye</t>
   </si>
   <si>
@@ -508,9 +496,6 @@
     <t>Brown shrike, Red vented Bulbul</t>
   </si>
   <si>
-    <t>Banded bay Cuckoo, Yellow fronted Barbet, Hill Swallow, Brown capped Babbler, Scimitter Babbler, Sri Lankan whiteye</t>
-  </si>
-  <si>
     <t>Spurfowl, Black eagle, Yellow fronted Barbet, Scimitter Babbler, Pale billed Flowerpecker</t>
   </si>
   <si>
@@ -520,9 +505,6 @@
     <t>Brahminy kite, Barn Swallow</t>
   </si>
   <si>
-    <t>Jungle prinia, Large billed leaf wabbler, Sri Lankan whiteye</t>
-  </si>
-  <si>
     <t>Indian peafowl, Brown headed barbet, Crimson fronted Barbet, Copper smith Barbet, Black hooded Oriole, Brown capped Babbler, Brown breasted Flycatcher, Purple sunbird</t>
   </si>
   <si>
@@ -550,10 +532,28 @@
     <t>Black eagle, Yellow fronted Barbet, Zitting cisticola, Tickell's blue Flycatcher</t>
   </si>
   <si>
-    <t>Indian swiftlet, Yellow fronted Barbet, Orange minivet, Hill Swallow, Sri Lankan Swallow, Paddyfield Pipit, White rumped Shama, Grey-headed Canary Flycatcher</t>
-  </si>
-  <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Green Wabbler, Scimitter Babbler, Great tit</t>
+  </si>
+  <si>
+    <t>King quail, Black eagle, Brown headed barbet, Paddyfield Pipit, Zitting cisticola, Brown capped Babbler, Sri Lankan whiteye, Great tit</t>
+  </si>
+  <si>
+    <t>Yellow fronted Barbet, Brown capped Babbler, Great tit</t>
+  </si>
+  <si>
+    <t>Spotted Dove, Sri Lanka Hanging Parrot, Drongo cuckoo, Crimson fronted Barbet, Copper smith Barbet, Common Iora, Large billed leaf wabbler, White rumped Shama, Asian brown Flycatcher, Pale billed Flowerpecker, Great tit</t>
+  </si>
+  <si>
+    <t>Banded bay Cuckoo, Yellow fronted Barbet, Hill Swallow, Brown capped Babbler, Scimitter Babbler, Sri Lankan whiteye, Great tit</t>
+  </si>
+  <si>
+    <t>Jungle prinia, Large billed leaf wabbler, Sri Lankan whiteye, Great tit</t>
+  </si>
+  <si>
+    <t>Indian swiftlet, Yellow fronted Barbet, Orange minivet, Hill Swallow, Sri Lankan Swallow, Paddyfield Pipit, White rumped Shama, Grey-headed Canary Flycatcher, Great tit</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>6</v>
       </c>
       <c r="I108" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
@@ -4056,7 +4056,7 @@
         <v>4</v>
       </c>
       <c r="I109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
@@ -4085,7 +4085,7 @@
         <v>4</v>
       </c>
       <c r="I110" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -4114,7 +4114,7 @@
         <v>4</v>
       </c>
       <c r="I111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
@@ -4143,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="I112" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
@@ -4201,7 +4201,7 @@
         <v>5</v>
       </c>
       <c r="I114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
@@ -4230,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="I115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -4259,7 +4259,7 @@
         <v>5</v>
       </c>
       <c r="I116" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -4317,7 +4317,7 @@
         <v>5</v>
       </c>
       <c r="I118" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4346,7 +4346,7 @@
         <v>5</v>
       </c>
       <c r="I119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
@@ -4375,7 +4375,7 @@
         <v>3</v>
       </c>
       <c r="I120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
@@ -4404,7 +4404,7 @@
         <v>3</v>
       </c>
       <c r="I121" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>3</v>
       </c>
       <c r="I123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
@@ -4491,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="I124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
@@ -4549,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="I126" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
@@ -4578,7 +4578,7 @@
         <v>3</v>
       </c>
       <c r="I127" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -4607,7 +4607,7 @@
         <v>3</v>
       </c>
       <c r="I128" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -4636,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
@@ -4665,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
@@ -4694,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="I131" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -4752,7 +4752,7 @@
         <v>6</v>
       </c>
       <c r="I133" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
@@ -4781,7 +4781,7 @@
         <v>6</v>
       </c>
       <c r="I134" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -4810,7 +4810,7 @@
         <v>4</v>
       </c>
       <c r="I135" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
@@ -4839,7 +4839,7 @@
         <v>3</v>
       </c>
       <c r="I136" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
@@ -4897,7 +4897,7 @@
         <v>5</v>
       </c>
       <c r="I138" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
@@ -4955,7 +4955,7 @@
         <v>5</v>
       </c>
       <c r="I140" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
@@ -4984,7 +4984,7 @@
         <v>5</v>
       </c>
       <c r="I141" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -5013,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="I142" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
@@ -5100,7 +5100,7 @@
         <v>3</v>
       </c>
       <c r="I145" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -5129,7 +5129,7 @@
         <v>3</v>
       </c>
       <c r="I146" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
@@ -5158,7 +5158,7 @@
         <v>3</v>
       </c>
       <c r="I147" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -5187,7 +5187,7 @@
         <v>3</v>
       </c>
       <c r="I148" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
@@ -5245,7 +5245,7 @@
         <v>2</v>
       </c>
       <c r="I150" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -5274,7 +5274,7 @@
         <v>2</v>
       </c>
       <c r="I151" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -5303,7 +5303,7 @@
         <v>3</v>
       </c>
       <c r="I152" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
@@ -5332,7 +5332,7 @@
         <v>3</v>
       </c>
       <c r="I153" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
@@ -5390,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="I155" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -5419,7 +5419,7 @@
         <v>6</v>
       </c>
       <c r="I156" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
@@ -5448,7 +5448,7 @@
         <v>6</v>
       </c>
       <c r="I157" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
@@ -5506,7 +5506,7 @@
         <v>4</v>
       </c>
       <c r="I159" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -5564,7 +5564,7 @@
         <v>3</v>
       </c>
       <c r="I161" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
@@ -5622,7 +5622,7 @@
         <v>5</v>
       </c>
       <c r="I163" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -5680,7 +5680,7 @@
         <v>5</v>
       </c>
       <c r="I165" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -5709,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="I166" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -5767,7 +5767,7 @@
         <v>3</v>
       </c>
       <c r="I168" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -5796,7 +5796,7 @@
         <v>3</v>
       </c>
       <c r="I169" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
@@ -5825,7 +5825,7 @@
         <v>3</v>
       </c>
       <c r="I170" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
@@ -5854,7 +5854,7 @@
         <v>3</v>
       </c>
       <c r="I171" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -5883,7 +5883,7 @@
         <v>3</v>
       </c>
       <c r="I172" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -5941,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="I174" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -5970,7 +5970,7 @@
         <v>3</v>
       </c>
       <c r="I175" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -5999,7 +5999,7 @@
         <v>3</v>
       </c>
       <c r="I176" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
@@ -6028,7 +6028,7 @@
         <v>3</v>
       </c>
       <c r="I177" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -6057,7 +6057,7 @@
         <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -6115,7 +6115,7 @@
         <v>6</v>
       </c>
       <c r="I180" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
@@ -6144,7 +6144,7 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
@@ -6173,7 +6173,7 @@
         <v>3</v>
       </c>
       <c r="I182" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
@@ -6202,7 +6202,7 @@
         <v>5</v>
       </c>
       <c r="I183" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
@@ -6231,7 +6231,7 @@
         <v>5</v>
       </c>
       <c r="I184" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
@@ -6260,7 +6260,7 @@
         <v>3</v>
       </c>
       <c r="I185" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
@@ -6289,7 +6289,7 @@
         <v>3</v>
       </c>
       <c r="I186" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
@@ -6318,7 +6318,7 @@
         <v>2</v>
       </c>
       <c r="I187" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
@@ -6347,7 +6347,7 @@
         <v>3</v>
       </c>
       <c r="I188" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
@@ -6376,7 +6376,7 @@
         <v>3</v>
       </c>
       <c r="I189" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
@@ -6405,7 +6405,7 @@
         <v>6</v>
       </c>
       <c r="I190" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
